--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486801_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486801_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1356</v>
+        <v>5.137</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6287</v>
+        <v>3.5804</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5069</v>
+        <v>1.5566</v>
       </c>
       <c r="G2" t="n">
         <v>2.7314</v>
@@ -610,13 +610,13 @@
         <v>0.7723</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1987</v>
+        <v>0.2001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4411</v>
+        <v>0.3929</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2424</v>
+        <v>-0.1928</v>
       </c>
       <c r="V2" t="n">
         <v>1.4332</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9939</v>
+        <v>4.5621</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2058</v>
+        <v>3.6747</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7881</v>
+        <v>0.8874</v>
       </c>
       <c r="G3" t="n">
         <v>4.4046</v>
@@ -688,13 +688,13 @@
         <v>0.7723</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0369</v>
+        <v>-0.4688</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4139</v>
+        <v>0.0549</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.623</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.8193</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6652</v>
+        <v>2.3578</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3738</v>
+        <v>1.3396</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2914</v>
+        <v>1.0182</v>
       </c>
       <c r="G4" t="n">
         <v>3.7039</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5281</v>
+        <v>0.2207</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4338</v>
+        <v>0.3996</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.1789</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4084</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9948</v>
+        <v>0.872</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9406</v>
+        <v>0.8924</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0541</v>
+        <v>-0.0204</v>
       </c>
       <c r="G5" t="n">
         <v>1.4017</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0219</v>
+        <v>-0.1446</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2479</v>
+        <v>0.1997</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2698</v>
+        <v>-0.3443</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3505</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8047</v>
+        <v>0.6268</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6071</v>
+        <v>0.5037</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1977</v>
+        <v>0.1232</v>
       </c>
       <c r="G7" t="n">
         <v>0.9371</v>
@@ -1000,13 +1000,13 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3255</v>
+        <v>-0.5034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0555</v>
+        <v>-0.159</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2699</v>
+        <v>-0.3444</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0863</v>
+        <v>0.3339</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.5653</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8227</v>
+        <v>-0.2314</v>
       </c>
       <c r="G8" t="n">
-        <v>0.766</v>
+        <v>3.0745</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2204</v>
+        <v>2.4415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4544</v>
+        <v>0.633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7532</v>
+        <v>2.7169</v>
       </c>
       <c r="K8" t="n">
-        <v>1.359</v>
+        <v>1.8217</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6058</v>
+        <v>0.8952</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0128</v>
+        <v>0.3576</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1387</v>
+        <v>0.6198</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1514</v>
+        <v>-0.2623</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1708</v>
+        <v>-0.2965</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5243</v>
+        <v>0.3238</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3535</v>
+        <v>-0.6203</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1228</v>
+        <v>-0.8995</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1228</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0567</v>
+        <v>-0.0531</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4619</v>
+        <v>-0.5778</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4052</v>
+        <v>0.5248</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0745</v>
+        <v>0.766</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4415</v>
+        <v>1.2204</v>
       </c>
       <c r="I9" t="n">
-        <v>0.633</v>
+        <v>-0.4544</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7169</v>
+        <v>0.7532</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8217</v>
+        <v>1.359</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8952</v>
+        <v>-0.6058</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3576</v>
+        <v>0.0128</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6198</v>
+        <v>-0.1387</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2623</v>
+        <v>0.1514</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5446</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0892</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5737</v>
+        <v>-0.3101</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2204</v>
+        <v>-0.3657</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7941</v>
+        <v>0.0555</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8995</v>
+        <v>-0.1228</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5133</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0485</v>
+        <v>-1.381</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6899</v>
+        <v>-1.2211</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3586</v>
+        <v>-0.1599</v>
       </c>
       <c r="G11" t="n">
         <v>0.2398</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6053</v>
+        <v>-0.9377</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9657</v>
+        <v>-0.4969</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6395</v>
+        <v>-0.4409</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8415</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5576</v>
+        <v>-3.0487</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.275</v>
+        <v>-0.9648</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2826</v>
+        <v>-2.084</v>
       </c>
       <c r="G12" t="n">
         <v>1.3882</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6329</v>
+        <v>-1.124</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8554</v>
+        <v>-0.5451</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7775</v>
+        <v>-0.5789</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5406</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.3904</v>
+        <v>9.666099999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>8.2684</v>
+        <v>8.5442</v>
       </c>
       <c r="F13" t="n">
-        <v>1.122</v>
+        <v>1.121999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>19.4128</v>
@@ -1468,13 +1468,13 @@
         <v>10.6191</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.861</v>
+        <v>-3.5851</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6924000000000002</v>
+        <v>-0.4166000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.1684</v>
+        <v>-3.1687</v>
       </c>
       <c r="V13" t="n">
         <v>-5.196400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.97</v>
+        <v>2.8981</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7191</v>
+        <v>3.2362</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7491</v>
+        <v>-0.3381</v>
       </c>
       <c r="G14" t="n">
         <v>-5.0508</v>
@@ -1546,13 +1546,13 @@
         <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3697</v>
+        <v>0.5584</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0557</v>
+        <v>0.4615</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3141</v>
+        <v>0.097</v>
       </c>
       <c r="V14" t="n">
         <v>5.0736</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3496</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.312</v>
+        <v>-0.4124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0376</v>
+        <v>-0.1787</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.0292</v>
+        <v>-0.5817</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.6478</v>
+        <v>-0.6901</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3813</v>
+        <v>0.1084</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.8762</v>
+        <v>0.2883</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.9576</v>
+        <v>0.2069</v>
       </c>
       <c r="L15" t="n">
         <v>0.0814</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.153</v>
+        <v>-0.87</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6903</v>
+        <v>-0.897</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4627</v>
+        <v>0.0271</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7416</v>
+        <v>-0.1723</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9025</v>
+        <v>-0.0209</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8391</v>
+        <v>-0.1514</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2856</v>
+        <v>0.1628</v>
       </c>
       <c r="W15" t="n">
         <v>0.2856</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>J. SECO YANES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7773</v>
+        <v>-0.6679</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7227</v>
+        <v>-0.4965</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0546</v>
+        <v>-0.1713</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5817</v>
+        <v>-1.4897</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6901</v>
+        <v>-0.6691</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1084</v>
+        <v>-0.8206</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2883</v>
+        <v>-0.6688</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2069</v>
+        <v>0.0207</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>-0.6895</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.87</v>
+        <v>-0.8209</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.897</v>
+        <v>-0.6898</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0271</v>
+        <v>-0.1311</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3584</v>
+        <v>0.3654</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3312</v>
+        <v>0.1723</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0272</v>
+        <v>0.1931</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1628</v>
+        <v>-0.1228</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.1228</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SECO YANES</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9285</v>
+        <v>-0.7854</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8068</v>
+        <v>-0.8257</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1217</v>
+        <v>0.0403</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4897</v>
+        <v>-4.0292</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6691</v>
+        <v>-2.6478</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8206</v>
+        <v>-1.3813</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6688</v>
+        <v>-1.8762</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0207</v>
+        <v>-1.9576</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6895</v>
+        <v>0.0814</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8209</v>
+        <v>-2.153</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6898</v>
+        <v>-0.6903</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1311</v>
+        <v>-1.4627</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1048</v>
+        <v>1.6066</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.138</v>
+        <v>0.7649</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2428</v>
+        <v>0.8417</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1228</v>
+        <v>0.2856</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1697</v>
+        <v>-0.869</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1764</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9933</v>
+        <v>-0.6927</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3293</v>
@@ -1858,13 +1858,13 @@
         <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5957</v>
+        <v>0.8963</v>
       </c>
       <c r="T18" t="n">
         <v>0.3856</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2101</v>
+        <v>0.5107</v>
       </c>
       <c r="V18" t="n">
         <v>-0.243</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2196</v>
+        <v>-1.2492</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9225</v>
+        <v>1.678</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1421</v>
+        <v>-2.9272</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.8539</v>
+        <v>-0.002</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9097</v>
+        <v>0.7667</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9442</v>
+        <v>-0.7687</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4661</v>
+        <v>3.6479</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3916</v>
+        <v>1.7331</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0745</v>
+        <v>1.9148</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3878</v>
+        <v>-3.6499</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5181</v>
+        <v>-0.9664</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8697</v>
+        <v>-2.6835</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1239</v>
+        <v>0.3862</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8616</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>2.3169</v>
       </c>
       <c r="S19" t="n">
-        <v>2.631</v>
+        <v>0.3309</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5092</v>
+        <v>0.2891</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1218</v>
+        <v>0.0418</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1271</v>
+        <v>-1.9643</v>
       </c>
       <c r="W19" t="n">
-        <v>2.741</v>
+        <v>-0.3282</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6138</v>
+        <v>-1.6361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>P. JIMÉNEZ VELÁZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4958</v>
+        <v>-2.1455</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6437</v>
+        <v>-1.3866</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1396</v>
+        <v>-0.7589</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.002</v>
+        <v>-2.2006</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7667</v>
+        <v>-0.8759</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7687</v>
+        <v>-1.3247</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6479</v>
+        <v>-1.3176</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7331</v>
+        <v>-0.6688</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9148</v>
+        <v>-0.6488</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.6499</v>
+        <v>-0.883</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9664</v>
+        <v>-0.2071</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.6835</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3169</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9157</v>
+        <v>0.0551</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7451</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1706</v>
+        <v>0.1242</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.9643</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5543</v>
+        <v>-2.1847</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.42</v>
+        <v>-2.2132</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1343</v>
+        <v>0.0285</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8759</v>
@@ -2092,13 +2092,13 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2041</v>
+        <v>0.1655</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0828</v>
+        <v>0.124</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1212</v>
+        <v>0.0415</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1228</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. JIMÉNEZ VELÁZQUEZ</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5647</v>
+        <v>-2.4165</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5935</v>
+        <v>-0.5254</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-1.8911</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2006</v>
+        <v>-3.8539</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8759</v>
+        <v>-1.9097</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3247</v>
+        <v>-1.9442</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3176</v>
+        <v>-0.4661</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6688</v>
+        <v>-0.3916</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6488</v>
+        <v>-0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.883</v>
+        <v>-3.3878</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2071</v>
+        <v>-1.5181</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.8697</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3641</v>
+        <v>1.4341</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2759</v>
+        <v>1.0613</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0882</v>
+        <v>0.3728</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.390300000000002</v>
+        <v>-8.011299999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1221</v>
+        <v>-1.122</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.2684</v>
+        <v>-6.8892</v>
       </c>
       <c r="G23" t="n">
         <v>-19.4131</v>
@@ -2221,13 +2221,13 @@
         <v>-8.7264</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.851600000000001</v>
+        <v>-1.8516</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.4059</v>
+        <v>-2.405899999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5541</v>
+        <v>0.5540999999999998</v>
       </c>
       <c r="M23" t="n">
         <v>-17.5614</v>
@@ -2248,13 +2248,13 @@
         <v>11.5845</v>
       </c>
       <c r="S23" t="n">
-        <v>3.861099999999999</v>
+        <v>5.24</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1686</v>
+        <v>3.1687</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6924999999999999</v>
+        <v>2.0714</v>
       </c>
       <c r="V23" t="n">
         <v>5.196199999999999</v>
